--- a/task120/golden/campus_water_capacity_2027.xlsx
+++ b/task120/golden/campus_water_capacity_2027.xlsx
@@ -82,7 +82,7 @@
     <t>Firm capacity is the total of the wells' most recent pump-test capacities less Well 1, the largest: W1 1,090, W2 820, W3 760, W4 700, W5 640 gpm.</t>
   </si>
   <si>
-    <t>Maximum day demand is the day's well production less the water the four tanks gained between that day's midnights (here they gave water up), counting water lost from the mains as used.</t>
+    <t>Water used on a day is a balance over the whole system: the wells' production less the water the four tanks gained between that day's midnights (on this day they gave water up); the mains' losses are inside it.</t>
   </si>
   <si>
     <t>The largest day of well production alone was August 21 (4,136,417 gal), when the wells refilled the tanks.</t>
